--- a/panchang-data/Dwaraka2026.xlsx
+++ b/panchang-data/Dwaraka2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5397">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16216,6 +16216,9 @@
   </si>
   <si>
     <t>121°05'00.44</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16705,7 +16708,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16791,7 +16794,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>51</v>
@@ -16877,7 +16880,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16963,7 +16966,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>90</v>
@@ -17049,7 +17052,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17135,7 +17138,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>126</v>
@@ -17221,7 +17224,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>144</v>
@@ -17307,7 +17310,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17393,7 +17396,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>51</v>
@@ -17479,7 +17482,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17565,7 +17568,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>90</v>
@@ -17651,7 +17654,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17737,7 +17740,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>126</v>
@@ -17823,7 +17826,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>144</v>
@@ -17909,7 +17912,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17995,7 +17998,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>51</v>
@@ -18081,7 +18084,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18167,7 +18170,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>90</v>
@@ -18253,7 +18256,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18339,7 +18342,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>126</v>
@@ -18425,7 +18428,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>144</v>
@@ -18511,7 +18514,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18597,7 +18600,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>51</v>
@@ -18683,7 +18686,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18769,7 +18772,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>90</v>
@@ -18855,7 +18858,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18941,7 +18944,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>126</v>
@@ -19027,7 +19030,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>144</v>
@@ -19113,7 +19116,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19199,7 +19202,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>51</v>
@@ -19285,7 +19288,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19371,7 +19374,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>90</v>
@@ -19457,7 +19460,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19543,7 +19546,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>126</v>
@@ -19629,7 +19632,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>144</v>
@@ -19715,7 +19718,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19801,7 +19804,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>51</v>
@@ -19887,7 +19890,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19973,7 +19976,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>90</v>
@@ -20059,7 +20062,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20145,7 +20148,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>126</v>
@@ -20231,7 +20234,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>144</v>
@@ -20317,7 +20320,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20403,7 +20406,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>51</v>
@@ -20489,7 +20492,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20575,7 +20578,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>90</v>
@@ -20661,7 +20664,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20747,7 +20750,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>126</v>
@@ -20833,7 +20836,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>144</v>
@@ -20919,7 +20922,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21005,7 +21008,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>51</v>
@@ -21091,7 +21094,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21177,7 +21180,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>90</v>
@@ -21263,7 +21266,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21349,7 +21352,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>126</v>
@@ -21435,7 +21438,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>144</v>
@@ -21521,7 +21524,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21607,7 +21610,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>51</v>
@@ -21693,7 +21696,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21779,7 +21782,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>90</v>
@@ -21865,7 +21868,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21951,7 +21954,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>126</v>
@@ -22037,7 +22040,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>144</v>
@@ -22123,7 +22126,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22209,7 +22212,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>51</v>
@@ -22295,7 +22298,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22381,7 +22384,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>90</v>
@@ -22467,7 +22470,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22553,7 +22556,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>126</v>
@@ -22639,7 +22642,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>144</v>
@@ -22725,7 +22728,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22811,7 +22814,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>51</v>
@@ -22897,7 +22900,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22983,7 +22986,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>90</v>
@@ -23069,7 +23072,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23155,7 +23158,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>126</v>
@@ -23241,7 +23244,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>144</v>
@@ -23327,7 +23330,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23413,7 +23416,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>51</v>
@@ -23499,7 +23502,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23585,7 +23588,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>90</v>
@@ -23671,7 +23674,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23757,7 +23760,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>126</v>
@@ -23843,7 +23846,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>144</v>
@@ -23929,7 +23932,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24015,7 +24018,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>51</v>
@@ -24101,7 +24104,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24187,7 +24190,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>90</v>
@@ -24273,7 +24276,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24359,7 +24362,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>126</v>
@@ -24445,7 +24448,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1010</v>
+        <v>1437</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>144</v>
@@ -24531,7 +24534,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24617,7 +24620,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>51</v>
@@ -24703,7 +24706,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24789,7 +24792,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>90</v>
@@ -24875,7 +24878,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24961,7 +24964,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>126</v>
@@ -25047,7 +25050,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>144</v>
@@ -25133,7 +25136,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25219,7 +25222,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>51</v>
@@ -25305,7 +25308,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25391,7 +25394,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>90</v>
@@ -25477,7 +25480,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25563,7 +25566,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>126</v>
@@ -25649,7 +25652,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>144</v>
@@ -25735,7 +25738,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25821,7 +25824,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>51</v>
@@ -25907,7 +25910,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25993,7 +25996,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>90</v>
@@ -26079,7 +26082,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26165,7 +26168,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>126</v>
@@ -26251,7 +26254,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>144</v>
@@ -26337,7 +26340,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26423,7 +26426,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>51</v>
@@ -26509,7 +26512,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26595,7 +26598,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>90</v>
@@ -26681,7 +26684,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26767,7 +26770,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>126</v>
@@ -26853,7 +26856,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>144</v>
@@ -26939,7 +26942,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27025,7 +27028,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1437</v>
+        <v>1876</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>51</v>
@@ -27111,7 +27114,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27197,7 +27200,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>90</v>
@@ -27283,7 +27286,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27369,7 +27372,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>126</v>
@@ -27455,7 +27458,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>144</v>
@@ -27541,7 +27544,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27627,7 +27630,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>51</v>
@@ -27713,7 +27716,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27799,7 +27802,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>90</v>
@@ -27885,7 +27888,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27971,7 +27974,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>126</v>
@@ -28057,7 +28060,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>144</v>
@@ -28143,7 +28146,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28229,7 +28232,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>51</v>
@@ -28315,7 +28318,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28401,7 +28404,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>90</v>
@@ -28487,7 +28490,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28573,7 +28576,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>126</v>
@@ -28659,7 +28662,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>144</v>
@@ -28745,7 +28748,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28831,7 +28834,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>51</v>
@@ -28917,7 +28920,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29003,7 +29006,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>90</v>
@@ -29089,7 +29092,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29175,7 +29178,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>126</v>
@@ -29261,7 +29264,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>144</v>
@@ -29347,7 +29350,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29433,7 +29436,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>51</v>
@@ -29519,7 +29522,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29605,7 +29608,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1876</v>
+        <v>5396</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>90</v>
@@ -29691,7 +29694,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29777,7 +29780,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>126</v>
@@ -29863,7 +29866,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>144</v>
@@ -29949,7 +29952,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30035,7 +30038,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>51</v>
@@ -30121,7 +30124,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30207,7 +30210,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>90</v>
@@ -30293,7 +30296,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30379,7 +30382,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>126</v>
@@ -30465,7 +30468,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>144</v>
@@ -30551,7 +30554,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30637,7 +30640,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>51</v>
@@ -30723,7 +30726,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30809,7 +30812,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>90</v>
@@ -30895,7 +30898,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2312</v>
+        <v>5396</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
